--- a/budget/budget.xlsx
+++ b/budget/budget.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -505,14 +505,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PRESUPUESTO DE PUESTA EN MARCHA (PILOTO INICIAL) -- HIDRO-VIGIA</t>
+          <t>PRESUPUESTO DE PUESTA EN MARCHA (PILOTO INICIAL) -- RALLY STUDIO</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Equipo: Mentes Pinoleras | Moneda base: Dolares Estadounidenses (USD) | Metodologia: Costos mayoristas sustentados</t>
+          <t>Equipo: Equipo UNI Test | Moneda base: Dólares estadounidenses (USD) | Metodologia: Costos mayoristas sustentados</t>
         </is>
       </c>
     </row>
